--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/698182</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115820470</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89899712</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134875215</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1270,6 +1295,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112636772</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126702838</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1505,6 +1540,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63211281</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1614,6 +1654,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67536480</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1723,6 +1768,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91379377</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,8 +1882,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91379371</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,60 +801,58 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115820470</v>
+        <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>103024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1906</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revig blodrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Potentilla anglica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Laichard.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Hästhagen, 400 m VNV , Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397523</v>
+        <v>397531</v>
       </c>
       <c r="R3" t="n">
-        <v>6199525</v>
+        <v>6199545</v>
       </c>
       <c r="S3" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,24 +874,24 @@
           <t>Stehag</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>M-Esv-0047</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Huvudbeståndet på nya koordinater. Enstaka plantor upp till 150 meter norr om punkt längs kant av skogsväg. Exemplar delvis svårbedömda, misstänker vissa vara hybrider Skogsavverkning pågår, flera virkeshögar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,88 +900,88 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonny Johansson</t>
+          <t>Helen Schellenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonny Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Helen Schellenberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115820470</t>
+          <t>https://artportalen.se/Sighting/136092112</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89899712</v>
+        <v>115820470</v>
       </c>
       <c r="B4" t="n">
-        <v>43071</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101167</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Förgyllt metallfly</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lamprotes c-aureum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Knoch, 1781)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skoghus, Stehag, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397512</v>
+        <v>397523</v>
       </c>
       <c r="R4" t="n">
-        <v>6199886</v>
+        <v>6199525</v>
       </c>
       <c r="S4" t="n">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,17 +1005,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1981-05-29</t>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1981-05-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Kläckta 1981-06 - 16-20</t>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,39 +1029,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Christer Bergendorff</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christer Bergendorff</t>
+          <t>Jonny Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christer Bergendorff</t>
+          <t>Jonny Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89899712</t>
+          <t>https://artportalen.se/Sighting/115820470</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134875215</v>
+        <v>89899712</v>
       </c>
       <c r="B5" t="n">
-        <v>43076</v>
+        <v>43071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,39 +1082,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stockamöllan.., Sk</t>
+          <t>Skoghus, Stehag, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397479</v>
+        <v>397512</v>
       </c>
       <c r="R5" t="n">
-        <v>6200075</v>
+        <v>6199886</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,12 +1134,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1973-07-24</t>
+          <t>1981-05-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1973-07-24</t>
+          <t>1981-05-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kläckta 1981-06 - 16-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,80 +1157,94 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Christer Bergendorff</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hans Hellberg</t>
+          <t>Christer Bergendorff</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Hellberg</t>
+          <t>Christer Bergendorff</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134875215</t>
+          <t>https://artportalen.se/Sighting/89899712</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112636772</v>
+        <v>134875215</v>
       </c>
       <c r="B6" t="n">
-        <v>58327</v>
+        <v>43076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>101167</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Förgyllt metallfly</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lamprotes c-aureum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Knoch, 1781)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Stockamöllan.., Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397523</v>
+        <v>397479</v>
       </c>
       <c r="R6" t="n">
-        <v>6199525</v>
+        <v>6200075</v>
       </c>
       <c r="S6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,22 +1268,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>1973-07-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>1973-07-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,50 +1282,51 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jonny Johansson</t>
+          <t>Hans Hellberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonny Johansson</t>
+          <t>Hans Hellberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112636772</t>
+          <t>https://artportalen.se/Sighting/134875215</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126702838</v>
+        <v>112636772</v>
       </c>
       <c r="B7" t="n">
-        <v>58602</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1380,22 +1383,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,54 +1424,66 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126702838</t>
+          <t>https://artportalen.se/Sighting/112636772</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>63211281</v>
+        <v>126702838</v>
       </c>
       <c r="B8" t="n">
-        <v>97983</v>
+        <v>58602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>900m NNO Sonarps gård, Sk</t>
+          <t>Hästhagen, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>395678</v>
+        <v>397523</v>
       </c>
       <c r="R8" t="n">
-        <v>6198242</v>
+        <v>6199525</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,22 +1502,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Bosarp</t>
+          <t>Stehag</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1993-04-28</t>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1993-04-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum/3C0j1603/Bosarp s:n/THt/ /Tord Holmstedt,Viken</t>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,62 +1533,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>kärr i gles aspdunge</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>SkFlora    497455</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Jonny Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63211281</t>
+          <t>https://artportalen.se/Sighting/126702838</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67536480</v>
+        <v>63211281</v>
       </c>
       <c r="B9" t="n">
-        <v>107043</v>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1654</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Veronica montana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1577,26 +1583,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hjortsås, norr om, Sk</t>
+          <t>900m NNO Sonarps gård, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>396757</v>
+        <v>395678</v>
       </c>
       <c r="R9" t="n">
-        <v>6198293</v>
+        <v>6198242</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,17 +1614,22 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Stehag</t>
+          <t>Bosarp</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-09-12</t>
+          <t>1993-04-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-09-12</t>
+          <t>1993-04-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum/3C0j1603/Bosarp s:n/THt/ /Tord Holmstedt,Viken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,83 +1643,87 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Bokskog, vägkant</t>
+          <t>kärr i gles aspdunge</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>SkFlora    497455</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Via Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67536480</t>
+          <t>https://artportalen.se/Sighting/63211281</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91379377</v>
+        <v>67536480</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>107043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1654</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica montana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skär, Bosarp Eslöv, Sk</t>
+          <t>Hjortsås, norr om, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>396273</v>
+        <v>396757</v>
       </c>
       <c r="R10" t="n">
-        <v>6197627</v>
+        <v>6198293</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1734,17 +1742,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Bosarp</t>
+          <t>Stehag</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2017-09-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2017-09-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,58 +1763,63 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Bokskog, vägkant</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Andersson</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Andersson</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91379377</t>
+          <t>https://artportalen.se/Sighting/67536480</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91379371</v>
+        <v>91379377</v>
       </c>
       <c r="B11" t="n">
-        <v>58676</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1883,6 +1896,120 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91379377</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>91379371</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skär, Bosarp Eslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>396273</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6197627</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bosarp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91379371</t>
         </is>
@@ -1900,6 +2027,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103024</v>
+        <v>103026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103026</v>
+        <v>103027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103027</v>
+        <v>103028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103028</v>
+        <v>103034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103034</v>
+        <v>103035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103035</v>
+        <v>103046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103046</v>
+        <v>103059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103059</v>
+        <v>103060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103060</v>
+        <v>103073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103073</v>
+        <v>103074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
